--- a/artfynd/A 10226-2023 artfynd.xlsx
+++ b/artfynd/A 10226-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122825198</v>
+        <v>122825158</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,33 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -773,11 +773,6 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>trummar i söder</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122825158</v>
+        <v>122825198</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,33 +815,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -902,6 +897,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>trummar i söder</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 10226-2023 artfynd.xlsx
+++ b/artfynd/A 10226-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122825158</v>
+        <v>122825198</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,33 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -773,6 +773,11 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>trummar i söder</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122825198</v>
+        <v>122825158</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,33 +820,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -897,11 +902,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>trummar i söder</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 10226-2023 artfynd.xlsx
+++ b/artfynd/A 10226-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122825198</v>
+        <v>122825158</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>57634</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,33 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -773,11 +773,6 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>trummar i söder</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122825158</v>
+        <v>122825198</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,33 +815,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -902,6 +897,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>trummar i söder</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 10226-2023 artfynd.xlsx
+++ b/artfynd/A 10226-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122825158</v>
+        <v>122825198</v>
       </c>
       <c r="B2" t="n">
-        <v>57634</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,33 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -773,6 +773,11 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>trummar i söder</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122825198</v>
+        <v>122825158</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
+        <v>57634</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,33 +820,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -897,11 +902,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>trummar i söder</t>
         </is>
       </c>
       <c r="AD3" t="b">
